--- a/Entrega-2/v4/demo/generated/master_proposal.xlsx
+++ b/Entrega-2/v4/demo/generated/master_proposal.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookProtection workbookPassword="FE27" lockStructure="1"/>
   <sheets>
-    <sheet name="Proposal" sheetId="1" ns1:id="R2c322b22fb1c4de5"/>
+    <sheet name="Proposal" sheetId="1" ns1:id="Rac8af5d0fcd1416f"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
